--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_269_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_269_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1769</v>
+        <v>5.6059</v>
       </c>
       <c r="E2" t="n">
-        <v>2.664</v>
+        <v>3.757</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5129</v>
+        <v>1.849</v>
       </c>
       <c r="G2" t="n">
         <v>2.0681</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2107</v>
+        <v>0.2183</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.963</v>
+        <v>0.13</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2478</v>
+        <v>0.0883</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9635</v>
+        <v>3.6774</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8796</v>
+        <v>0.5947</v>
       </c>
       <c r="F3" t="n">
-        <v>2.084</v>
+        <v>3.0827</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.5757</v>
+        <v>0.1402</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.4542</v>
+        <v>-4.4838</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1215</v>
+        <v>4.624</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.182</v>
+        <v>0.6808</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5384</v>
+        <v>-2.7386</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.6436</v>
+        <v>3.4193</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3937</v>
+        <v>-0.5405</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9157</v>
+        <v>-1.7452</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5221</v>
+        <v>1.2046</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>3.4793</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>3.4793</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3948</v>
+        <v>0.1997</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2546</v>
+        <v>-0.0861</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1401</v>
+        <v>0.2858</v>
       </c>
       <c r="V3" t="n">
-        <v>4.2888</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>4.9667</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7613</v>
+        <v>3.3799</v>
       </c>
       <c r="E4" t="n">
-        <v>3.089</v>
+        <v>3.8271</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3277</v>
+        <v>-0.4472</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.541</v>
+        <v>0.9237</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0191</v>
+        <v>1.4056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5219</v>
+        <v>-0.4819</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3141</v>
+        <v>2.9037</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1141</v>
+        <v>2.1209</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4282</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8551</v>
+        <v>-1.98</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9049</v>
+        <v>-0.7153</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.2647</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8205</v>
+        <v>-0.0077</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7027</v>
+        <v>-0.2906</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1177</v>
+        <v>0.2829</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5811</v>
+        <v>2.3955</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1627</v>
+        <v>0.2779</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5816</v>
+        <v>2.1176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9237</v>
+        <v>-4.5757</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4056</v>
+        <v>-2.4542</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4819</v>
+        <v>-2.1215</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9037</v>
+        <v>-4.182</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1209</v>
+        <v>-1.5384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7828000000000001</v>
+        <v>-2.6436</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.98</v>
+        <v>-0.3937</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7153</v>
+        <v>-0.9157</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2647</v>
+        <v>0.5221</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8066</v>
+        <v>0.8268</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.955</v>
+        <v>0.653</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1485</v>
+        <v>0.1737</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>4.2888</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>4.9667</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3342</v>
+        <v>1.8924</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6477000000000001</v>
+        <v>2.2201</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9819</v>
+        <v>-0.3277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1402</v>
+        <v>-1.541</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.4838</v>
+        <v>-1.0191</v>
       </c>
       <c r="I6" t="n">
-        <v>4.624</v>
+        <v>-0.5219</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6808</v>
+        <v>0.3141</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.7386</v>
+        <v>-0.1141</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4193</v>
+        <v>0.4282</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5405</v>
+        <v>-1.8551</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7452</v>
+        <v>-0.9049</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2046</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4793</v>
+        <v>2.0876</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4793</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1435</v>
+        <v>0.9515</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3285</v>
+        <v>0.8338</v>
       </c>
       <c r="U6" t="n">
-        <v>0.185</v>
+        <v>0.1177</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.246</v>
+        <v>-0.043</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4376</v>
+        <v>-0.8438</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1916</v>
+        <v>0.8008</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7257</v>
+        <v>-1.7758</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6253</v>
+        <v>-0.24</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1004</v>
+        <v>-1.5358</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4287</v>
+        <v>0.0366</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7527</v>
+        <v>0.6757</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6391</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.297</v>
+        <v>-1.8123</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8726</v>
+        <v>-0.9157</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5756</v>
+        <v>-0.8966</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3199</v>
+        <v>0.3411</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9911</v>
+        <v>0.2794</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3289</v>
+        <v>0.0617</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.488</v>
+        <v>-0.3461</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1457</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3423</v>
+        <v>-0.2751</v>
       </c>
       <c r="G8" t="n">
         <v>0.0596</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1713</v>
+        <v>-0.0294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>-0.1415</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1023</v>
+        <v>-1.4189</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9368</v>
+        <v>-1.0392</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8344</v>
+        <v>-0.3797</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7758</v>
+        <v>-1.7257</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.24</v>
+        <v>-1.6253</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5358</v>
+        <v>-0.1004</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0366</v>
+        <v>-1.4287</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6757</v>
+        <v>-0.7527</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6391</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8123</v>
+        <v>-0.297</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9157</v>
+        <v>-0.8726</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>0.5756</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7183</v>
+        <v>1.147</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8136</v>
+        <v>0.3894</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0953</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5624</v>
+        <v>-2.0006</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5657</v>
+        <v>-2.0375</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0033</v>
+        <v>0.0369</v>
       </c>
       <c r="G10" t="n">
         <v>-2.611</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3528</v>
+        <v>-0.0854</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4876</v>
+        <v>0.0158</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8745</v>
+        <v>-3.1365</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8749</v>
+        <v>-2.2632</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9996</v>
+        <v>-0.8733</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9418</v>
+        <v>-3.6739</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7779</v>
+        <v>-0.7695</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1639</v>
+        <v>-2.9043</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6157</v>
+        <v>-2.2515</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2414</v>
+        <v>-0.7156</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6257</v>
+        <v>-1.5359</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3261</v>
+        <v>-1.4223</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5365</v>
+        <v>-0.0539</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7896</v>
+        <v>-1.3684</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6756</v>
+        <v>-0.0167</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9006</v>
+        <v>-0.0116</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2249</v>
+        <v>-0.005</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.397</v>
+        <v>-3.2551</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6917</v>
+        <v>-2.39</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7053</v>
+        <v>-0.8651</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6739</v>
+        <v>-2.9418</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7695</v>
+        <v>-2.7779</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9043</v>
+        <v>-0.1639</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2515</v>
+        <v>-1.6157</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7156</v>
+        <v>-2.2414</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5359</v>
+        <v>0.6257</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4223</v>
+        <v>-1.3261</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0539</v>
+        <v>-0.5365</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3684</v>
+        <v>-0.7896</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2772</v>
+        <v>0.295</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>0.3855</v>
       </c>
       <c r="U12" t="n">
-        <v>0.163</v>
+        <v>-0.0905</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0059</v>
+        <v>-4.1164</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7068</v>
+        <v>-1.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2992</v>
+        <v>-2.3664</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8996</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3602</v>
+        <v>0.2497</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3462</v>
+        <v>0.3029</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.140899999999999</v>
+        <v>2.634500000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2116</v>
+        <v>0.282100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.352399999999999</v>
+        <v>2.3525</v>
       </c>
       <c r="G14" t="n">
         <v>-19.5529</v>
@@ -1522,10 +1522,10 @@
         <v>-7.1657</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.801600000000001</v>
+        <v>-3.8016</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.364000000000001</v>
+        <v>-3.364</v>
       </c>
       <c r="M14" t="n">
         <v>-12.387</v>
@@ -1546,19 +1546,19 @@
         <v>19.7162</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5962</v>
+        <v>4.089899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9663999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6298</v>
+        <v>1.6297</v>
       </c>
       <c r="V14" t="n">
         <v>1.8608</v>
       </c>
       <c r="W14" t="n">
-        <v>8.466899999999999</v>
+        <v>8.466900000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-6.606100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3483</v>
+        <v>5.373</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1654</v>
+        <v>1.4577</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1829</v>
+        <v>3.9154</v>
       </c>
       <c r="G15" t="n">
         <v>4.6004</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>2.07</v>
+        <v>1.0947</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6844</v>
+        <v>-0.0233</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3856</v>
+        <v>1.118</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8838</v>
+        <v>5.1407</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1248</v>
+        <v>4.5966</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.241</v>
+        <v>0.544</v>
       </c>
       <c r="G16" t="n">
         <v>5.9957</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5578</v>
+        <v>-0.3009</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9709</v>
+        <v>-0.4991</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5869</v>
+        <v>0.1981</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7073</v>
+        <v>2.7688</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5374</v>
+        <v>1.1835</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1699</v>
+        <v>1.5852</v>
       </c>
       <c r="G17" t="n">
         <v>1.738</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2473</v>
+        <v>-0.1858</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4955</v>
+        <v>0.1417</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7429</v>
+        <v>-0.3275</v>
       </c>
       <c r="V17" t="n">
         <v>2.1444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4118</v>
+        <v>0.305</v>
       </c>
       <c r="E18" t="n">
-        <v>1.266</v>
+        <v>0.5905</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8542</v>
+        <v>-0.2854</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1408</v>
+        <v>2.2986</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3649</v>
+        <v>2.1345</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2241</v>
+        <v>0.1641</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9941</v>
+        <v>2.0378</v>
       </c>
       <c r="K18" t="n">
-        <v>3.529</v>
+        <v>1.4991</v>
       </c>
       <c r="L18" t="n">
-        <v>0.465</v>
+        <v>0.5386</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1467</v>
+        <v>0.2608</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8358</v>
+        <v>0.6354</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6891</v>
+        <v>-0.3746</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.0154</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5004</v>
+        <v>0.0244</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7512</v>
+        <v>-0.3418</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2508</v>
+        <v>0.3662</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3745</v>
+        <v>0.2203</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6891</v>
+        <v>-1.4532</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3146</v>
+        <v>1.6735</v>
       </c>
       <c r="G19" t="n">
         <v>1.048</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4946</v>
+        <v>0.1002</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2038</v>
+        <v>0.1551</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.1329</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1187</v>
+        <v>0.4403</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6564</v>
+        <v>-0.5733</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2986</v>
+        <v>4.1408</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1345</v>
+        <v>4.3649</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1641</v>
+        <v>-0.2241</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0378</v>
+        <v>3.9941</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4991</v>
+        <v>3.529</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5386</v>
+        <v>0.465</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2608</v>
+        <v>0.1467</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6354</v>
+        <v>0.8358</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3746</v>
+        <v>-0.6891</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6237</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8184</v>
+        <v>-0.0444</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-0.0745</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0048</v>
+        <v>0.0301</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1814</v>
+        <v>-1.3126</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3648</v>
+        <v>-0.9076</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1834</v>
+        <v>-0.4049</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6472</v>
+        <v>-0.0485</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1224</v>
+        <v>0.7277</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7696</v>
+        <v>-0.7762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.104</v>
+        <v>-0.3524</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0672</v>
+        <v>-0.2654</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>-0.0871</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5432</v>
+        <v>0.304</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1896</v>
+        <v>0.9931</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7328</v>
+        <v>-0.6891</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3195</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5091</v>
+        <v>-0.5682</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.4676</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3598</v>
+        <v>-0.1006</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.317</v>
+        <v>-1.8954</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2615</v>
+        <v>-2.2469</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0555</v>
+        <v>0.3515</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0485</v>
+        <v>0.6472</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7277</v>
+        <v>-0.1224</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7762</v>
+        <v>0.7696</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3524</v>
+        <v>0.104</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2654</v>
+        <v>0.0672</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0871</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>0.304</v>
+        <v>0.5432</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9931</v>
+        <v>-0.1896</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6891</v>
+        <v>0.7328</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5727</v>
+        <v>-0.2232</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>-0.0314</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7512</v>
+        <v>-0.1918</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6834</v>
+        <v>-2.5319</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8241</v>
+        <v>-1.7904</v>
       </c>
       <c r="G23" t="n">
         <v>0.7635</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3747</v>
+        <v>-0.2232</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3978</v>
+        <v>-6.7168</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.39</v>
+        <v>-5.272</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0078</v>
+        <v>-1.4447</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6308</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4081</v>
+        <v>0.0892</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7815</v>
+        <v>0.3446</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.140700000000002</v>
+        <v>1.2182</v>
       </c>
       <c r="E25" t="n">
         <v>-2.352500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2118</v>
+        <v>3.5709</v>
       </c>
       <c r="G25" t="n">
         <v>19.5529</v>
@@ -2380,7 +2380,7 @@
         <v>12.3871</v>
       </c>
       <c r="K25" t="n">
-        <v>8.941500000000001</v>
+        <v>8.941499999999998</v>
       </c>
       <c r="L25" t="n">
         <v>3.4455</v>
@@ -2404,13 +2404,13 @@
         <v>3.4795</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5961</v>
+        <v>-0.2372000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.63</v>
+        <v>-1.6299</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9664</v>
+        <v>1.3925</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8608</v>
